--- a/docs/培训/OpenWorker培训/01-质量周报/检验记录-热处理车间.xlsx
+++ b/docs/培训/OpenWorker培训/01-质量周报/检验记录-热处理车间.xlsx
@@ -506,11 +506,11 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P39R001</t>
+          <t>P40R001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,11 +552,11 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P39R002</t>
+          <t>P40R002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -598,11 +598,11 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P39R003</t>
+          <t>P40R003</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -652,11 +652,11 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P39R004</t>
+          <t>P40R004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,11 +698,11 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P39R005</t>
+          <t>P40R005</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -744,11 +744,11 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P39R006</t>
+          <t>P40R006</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -798,11 +798,11 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P39R007</t>
+          <t>P40R007</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -844,11 +844,11 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P39R008</t>
+          <t>P40R008</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -898,11 +898,11 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P39R009</t>
+          <t>P40R009</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -944,11 +944,11 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P39R010</t>
+          <t>P40R010</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
